--- a/R Markdown/resultados/tabelas_25_DA/df_integrado_2025_25_DA.xlsx
+++ b/R Markdown/resultados/tabelas_25_DA/df_integrado_2025_25_DA.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -377,42 +377,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>n_acoes</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>ano</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>idrgp_real</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>idrgp_diferenca</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>idrgp_var_percentual</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>valor_previsto</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>status_valor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>status_var_percentual</t>
-        </is>
-      </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>status_estatistico</t>
+          <t>status_detalhado</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>status_mapa</t>
         </is>
       </c>
     </row>
@@ -431,27 +436,39 @@
         <v>0.05427611013661751</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>180481051.88</v>
       </c>
       <c r="E2">
-        <v>2025</v>
+        <v>23</v>
+      </c>
+      <c r="F2">
+        <v>2025</v>
+      </c>
+      <c r="G2">
+        <v>0.03238126864284738</v>
+      </c>
+      <c r="H2">
+        <v>-0.02189484149377013</v>
       </c>
       <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.4033973959935409</v>
+      </c>
+      <c r="J2">
+        <v>302514690.1270415</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -470,27 +487,39 @@
         <v>0.0768001000600067</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>336699262.54</v>
       </c>
       <c r="E3">
-        <v>2025</v>
+        <v>22</v>
+      </c>
+      <c r="F3">
+        <v>2025</v>
+      </c>
+      <c r="G3">
+        <v>0.06040938457852886</v>
+      </c>
+      <c r="H3">
+        <v>-0.01639071548147784</v>
       </c>
       <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.2134204964403846</v>
+      </c>
+      <c r="J3">
+        <v>428054965.8569655</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -509,27 +538,39 @@
         <v>0.01518693116727706</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>198437703.51</v>
       </c>
       <c r="E4">
-        <v>2025</v>
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>2025</v>
+      </c>
+      <c r="G4">
+        <v>0.03560298723491132</v>
+      </c>
+      <c r="H4">
+        <v>0.02041605606763425</v>
       </c>
       <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr">
+        <v>1.344317416254857</v>
+      </c>
+      <c r="J4">
+        <v>84646260.84082605</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Valor previsto (R$) superado</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Muito acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -548,25 +589,37 @@
         <v>0.02852737800077722</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>167217155.17</v>
       </c>
       <c r="E5">
-        <v>2025</v>
+        <v>22</v>
+      </c>
+      <c r="F5">
+        <v>2025</v>
+      </c>
+      <c r="G5">
+        <v>0.03000150745382759</v>
+      </c>
+      <c r="H5">
+        <v>0.001474129453050373</v>
       </c>
       <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
+        <v>0.0516742005875973</v>
+      </c>
+      <c r="J5">
+        <v>159000910.2406158</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Valor previsto (R$) superado</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Dentro do IDRGP Alvo</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Dentro do IDRGP Alvo</t>
         </is>
@@ -587,27 +640,39 @@
         <v>0.01196759457375883</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>165788597.73</v>
       </c>
       <c r="E6">
-        <v>2025</v>
+        <v>25</v>
+      </c>
+      <c r="F6">
+        <v>2025</v>
+      </c>
+      <c r="G6">
+        <v>0.02974520075706069</v>
+      </c>
+      <c r="H6">
+        <v>0.01777760618330186</v>
       </c>
       <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
+        <v>1.485478645999804</v>
+      </c>
+      <c r="J6">
+        <v>66702885.57772348</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Valor previsto (R$) superado</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Muito acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -626,25 +691,37 @@
         <v>0.0146420577822676</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>96724806.43000001</v>
       </c>
       <c r="E7">
-        <v>2025</v>
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>2025</v>
+      </c>
+      <c r="G7">
+        <v>0.01735402087261617</v>
+      </c>
+      <c r="H7">
+        <v>0.002711963090348572</v>
       </c>
       <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr">
+        <v>0.1852173465421589</v>
+      </c>
+      <c r="J7">
+        <v>81609340.86240987</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Valor previsto (R$) superado</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Dentro do IDRGP Alvo</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Dentro do IDRGP Alvo</t>
         </is>
@@ -665,27 +742,39 @@
         <v>0.03106350078710079</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>70635388.02</v>
       </c>
       <c r="E8">
-        <v>2025</v>
+        <v>24</v>
+      </c>
+      <c r="F8">
+        <v>2025</v>
+      </c>
+      <c r="G8">
+        <v>0.01267315018026469</v>
+      </c>
+      <c r="H8">
+        <v>-0.0183903506068361</v>
       </c>
       <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.5920244061632854</v>
+      </c>
+      <c r="J8">
+        <v>173136307.8750016</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Muito abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -704,27 +793,39 @@
         <v>0.00780842708567104</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>91594945.72</v>
       </c>
       <c r="E9">
-        <v>2025</v>
+        <v>20</v>
+      </c>
+      <c r="F9">
+        <v>2025</v>
+      </c>
+      <c r="G9">
+        <v>0.01643363950282371</v>
+      </c>
+      <c r="H9">
+        <v>0.00862521241715267</v>
       </c>
       <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr">
+        <v>1.104603055457927</v>
+      </c>
+      <c r="J9">
+        <v>43521245.24501863</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Valor previsto (R$) superado</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Muito acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -743,27 +844,39 @@
         <v>0.02854078087441063</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>84333994.94</v>
       </c>
       <c r="E10">
-        <v>2025</v>
+        <v>20</v>
+      </c>
+      <c r="F10">
+        <v>2025</v>
+      </c>
+      <c r="G10">
+        <v>0.01513090552958645</v>
+      </c>
+      <c r="H10">
+        <v>-0.01340987534482418</v>
       </c>
       <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.4698496303879104</v>
+      </c>
+      <c r="J10">
+        <v>159075612.8335949</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -775,37 +888,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SÃ£o Miguel Paulista</t>
+          <t>São Miguel Paulista</t>
         </is>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.03997675152969091</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>48676742.54</v>
       </c>
       <c r="E11">
-        <v>2025</v>
+        <v>20</v>
+      </c>
+      <c r="F11">
+        <v>2025</v>
+      </c>
+      <c r="G11">
+        <v>0.008733408080392096</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>-0.03124334344929882</v>
       </c>
       <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.7815378252055885</v>
+      </c>
+      <c r="J11">
+        <v>222815425.9922034</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Muito abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -817,37 +939,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JaÃ§anÃ£/Tremembé</t>
+          <t>Jaçanã/Tremembé</t>
         </is>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.03619588619759224</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>77708608.54000001</v>
       </c>
       <c r="E12">
-        <v>2025</v>
+        <v>17</v>
+      </c>
+      <c r="F12">
+        <v>2025</v>
+      </c>
+      <c r="G12">
+        <v>0.01394220225771217</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>-0.02225368393988007</v>
       </c>
       <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.6148125181518663</v>
+      </c>
+      <c r="J12">
+        <v>201742300.0538679</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Muito abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -866,27 +997,39 @@
         <v>0.02290605900133662</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>79740030.13</v>
       </c>
       <c r="E13">
-        <v>2025</v>
+        <v>21</v>
+      </c>
+      <c r="F13">
+        <v>2025</v>
+      </c>
+      <c r="G13">
+        <v>0.01430667269683842</v>
+      </c>
+      <c r="H13">
+        <v>-0.008599386304498201</v>
       </c>
       <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.3754197220917142</v>
+      </c>
+      <c r="J13">
+        <v>127669785.5350936</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -905,27 +1048,39 @@
         <v>0.07049848664210395</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>136831474.89</v>
       </c>
       <c r="E14">
-        <v>2025</v>
+        <v>26</v>
+      </c>
+      <c r="F14">
+        <v>2025</v>
+      </c>
+      <c r="G14">
+        <v>0.02454981673176469</v>
+      </c>
+      <c r="H14">
+        <v>-0.04594866991033926</v>
       </c>
       <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.6517681740262669</v>
+      </c>
+      <c r="J14">
+        <v>392932135.1010609</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Muito abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -944,27 +1099,39 @@
         <v>0.03440060917127755</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>65629884.82</v>
       </c>
       <c r="E15">
-        <v>2025</v>
+        <v>20</v>
+      </c>
+      <c r="F15">
+        <v>2025</v>
+      </c>
+      <c r="G15">
+        <v>0.01177508059277359</v>
+      </c>
+      <c r="H15">
+        <v>-0.02262552857850396</v>
       </c>
       <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.6577072070396627</v>
+      </c>
+      <c r="J15">
+        <v>191736098.9473265</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Muito abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -976,32 +1143,44 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ButantÃ£</t>
+          <t>Butantã</t>
         </is>
       </c>
       <c r="C16">
         <v>0.03138103348631988</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>204758639.6</v>
       </c>
       <c r="E16">
-        <v>2025</v>
+        <v>26</v>
+      </c>
+      <c r="F16">
+        <v>2025</v>
+      </c>
+      <c r="G16">
+        <v>0.03673706711461331</v>
+      </c>
+      <c r="H16">
+        <v>0.005356033628293434</v>
       </c>
       <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr">
+        <v>0.1706774134965416</v>
+      </c>
+      <c r="J16">
+        <v>174906116.0994244</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>Valor previsto (R$) superado</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Dentro do IDRGP Alvo</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Dentro do IDRGP Alvo</t>
         </is>
@@ -1022,27 +1201,39 @@
         <v>0.01774539803593836</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1610729856.44</v>
       </c>
       <c r="E17">
-        <v>2025</v>
+        <v>40</v>
+      </c>
+      <c r="F17">
+        <v>2025</v>
+      </c>
+      <c r="G17">
+        <v>0.2889914240255958</v>
+      </c>
+      <c r="H17">
+        <v>0.2712460259896574</v>
       </c>
       <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr">
+        <v>15.28542923862988</v>
+      </c>
+      <c r="J17">
+        <v>98906196.0135055</v>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>Valor previsto (R$) superado</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Muito acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -1061,27 +1252,39 @@
         <v>0.04982071041328871</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>168677511.72</v>
       </c>
       <c r="E18">
-        <v>2025</v>
+        <v>27</v>
+      </c>
+      <c r="F18">
+        <v>2025</v>
+      </c>
+      <c r="G18">
+        <v>0.03026351943385159</v>
+      </c>
+      <c r="H18">
+        <v>-0.01955719097943712</v>
       </c>
       <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.3925514272518406</v>
+      </c>
+      <c r="J18">
+        <v>277681962.3707168</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -1093,34 +1296,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SÃ£o Mateus</t>
+          <t>São Mateus</t>
         </is>
       </c>
       <c r="C19">
         <v>0.05776210461891745</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>161650429.46</v>
       </c>
       <c r="E19">
-        <v>2025</v>
+        <v>22</v>
+      </c>
+      <c r="F19">
+        <v>2025</v>
+      </c>
+      <c r="G19">
+        <v>0.02900274531897254</v>
+      </c>
+      <c r="H19">
+        <v>-0.02875935929994491</v>
       </c>
       <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.4978932033325885</v>
+      </c>
+      <c r="J19">
+        <v>321944316.4938374</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -1139,27 +1354,39 @@
         <v>0.021319194803451</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>64191220.03</v>
       </c>
       <c r="E20">
-        <v>2025</v>
+        <v>14</v>
+      </c>
+      <c r="F20">
+        <v>2025</v>
+      </c>
+      <c r="G20">
+        <v>0.01151696047120553</v>
+      </c>
+      <c r="H20">
+        <v>-0.009802234332245462</v>
       </c>
       <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.459784453522548</v>
+      </c>
+      <c r="J20">
+        <v>118825199.401549</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -1178,25 +1405,37 @@
         <v>0.02476472440077774</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>161763597.72</v>
       </c>
       <c r="E21">
-        <v>2025</v>
+        <v>20</v>
+      </c>
+      <c r="F21">
+        <v>2025</v>
+      </c>
+      <c r="G21">
+        <v>0.02902304956582134</v>
+      </c>
+      <c r="H21">
+        <v>0.004258325165043604</v>
       </c>
       <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr">
+        <v>0.1719512438793735</v>
+      </c>
+      <c r="J21">
+        <v>138029289.6695368</v>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>Valor previsto (R$) superado</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Dentro do IDRGP Alvo</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Dentro do IDRGP Alvo</t>
         </is>
@@ -1217,27 +1456,39 @@
         <v>0.007949529934269608</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>105893712.17</v>
       </c>
       <c r="E22">
-        <v>2025</v>
+        <v>20</v>
+      </c>
+      <c r="F22">
+        <v>2025</v>
+      </c>
+      <c r="G22">
+        <v>0.01899907334120047</v>
+      </c>
+      <c r="H22">
+        <v>0.01104954340693086</v>
       </c>
       <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr">
+        <v>1.389961859165711</v>
+      </c>
+      <c r="J22">
+        <v>44307699.624531</v>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>Valor previsto (R$) superado</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Muito acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -1256,27 +1507,39 @@
         <v>0.01470567515443555</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>27409820.53</v>
       </c>
       <c r="E23">
-        <v>2025</v>
+        <v>16</v>
+      </c>
+      <c r="F23">
+        <v>2025</v>
+      </c>
+      <c r="G23">
+        <v>0.004917772546141275</v>
+      </c>
+      <c r="H23">
+        <v>-0.009787902608294279</v>
       </c>
       <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.6655867551475209</v>
+      </c>
+      <c r="J23">
+        <v>81963920.24511886</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Muito abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -1295,27 +1558,39 @@
         <v>0.006306371387863901</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>22743229.52</v>
       </c>
       <c r="E24">
-        <v>2025</v>
+        <v>13</v>
+      </c>
+      <c r="F24">
+        <v>2025</v>
+      </c>
+      <c r="G24">
+        <v>0.004080509378805693</v>
+      </c>
+      <c r="H24">
+        <v>-0.002225862009058208</v>
       </c>
       <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.3529544760623674</v>
+      </c>
+      <c r="J24">
+        <v>35149349.89673489</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -1334,27 +1609,39 @@
         <v>0.04188065349285796</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>117204155.13</v>
       </c>
       <c r="E25">
-        <v>2025</v>
+        <v>14</v>
+      </c>
+      <c r="F25">
+        <v>2025</v>
+      </c>
+      <c r="G25">
+        <v>0.02102835280373859</v>
+      </c>
+      <c r="H25">
+        <v>-0.02085230068911937</v>
       </c>
       <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.4978981689642301</v>
+      </c>
+      <c r="J25">
+        <v>233427061.7739499</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -1373,27 +1660,39 @@
         <v>0.03550998362496413</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>70022022.54000001</v>
       </c>
       <c r="E26">
-        <v>2025</v>
+        <v>21</v>
+      </c>
+      <c r="F26">
+        <v>2025</v>
+      </c>
+      <c r="G26">
+        <v>0.01256310232661336</v>
+      </c>
+      <c r="H26">
+        <v>-0.02294688129835077</v>
       </c>
       <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.6462092897789656</v>
+      </c>
+      <c r="J26">
+        <v>197919336.2546265</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Muito abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -1405,34 +1704,46 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Freguesia/BrasilÃ¢ndia</t>
+          <t>Freguesia/Brasilândia</t>
         </is>
       </c>
       <c r="C27">
         <v>0.04493881006046815</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>64235705.92</v>
       </c>
       <c r="E27">
-        <v>2025</v>
+        <v>22</v>
+      </c>
+      <c r="F27">
+        <v>2025</v>
+      </c>
+      <c r="G27">
+        <v>0.01152494197142343</v>
+      </c>
+      <c r="H27">
+        <v>-0.03341386808904472</v>
       </c>
       <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.7435414521231012</v>
+      </c>
+      <c r="J27">
+        <v>250472079.9980254</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Muito abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -1451,27 +1762,39 @@
         <v>0.03328667005479251</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>70721904.05</v>
       </c>
       <c r="E28">
-        <v>2025</v>
+        <v>22</v>
+      </c>
+      <c r="F28">
+        <v>2025</v>
+      </c>
+      <c r="G28">
+        <v>0.0126886725787667</v>
+      </c>
+      <c r="H28">
+        <v>-0.02059799747602581</v>
       </c>
       <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.6188061900490456</v>
+      </c>
+      <c r="J28">
+        <v>185527419.9208516</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Muito abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -1483,34 +1806,46 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aricanduva/Formosa/CarrÃ£o</t>
+          <t>Aricanduva/Formosa/Carrão</t>
         </is>
       </c>
       <c r="C29">
         <v>0.01278087722546964</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>30436283.97</v>
       </c>
       <c r="E29">
-        <v>2025</v>
+        <v>17</v>
+      </c>
+      <c r="F29">
+        <v>2025</v>
+      </c>
+      <c r="G29">
+        <v>0.005460769856205468</v>
+      </c>
+      <c r="H29">
+        <v>-0.007320107369264174</v>
       </c>
       <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.5727390413137461</v>
+      </c>
+      <c r="J29">
+        <v>71235818.18377644</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Muito abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -1529,27 +1864,39 @@
         <v>0.01442360309469943</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>102049762.94</v>
       </c>
       <c r="E30">
-        <v>2025</v>
+        <v>20</v>
+      </c>
+      <c r="F30">
+        <v>2025</v>
+      </c>
+      <c r="G30">
+        <v>0.01830940563719763</v>
+      </c>
+      <c r="H30">
+        <v>0.0038858025424982</v>
       </c>
       <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30" t="inlineStr">
+        <v>0.2694058146903809</v>
+      </c>
+      <c r="J30">
+        <v>80391756.33120196</v>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>Valor previsto (R$) superado</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -1568,27 +1915,39 @@
         <v>0.01471389456597418</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>173955689.05</v>
       </c>
       <c r="E31">
-        <v>2025</v>
+        <v>19</v>
+      </c>
+      <c r="F31">
+        <v>2025</v>
+      </c>
+      <c r="G31">
+        <v>0.03121051124427696</v>
+      </c>
+      <c r="H31">
+        <v>0.01649661667830278</v>
       </c>
       <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31" t="inlineStr">
+        <v>1.121159092471081</v>
+      </c>
+      <c r="J31">
+        <v>82009732.16362916</v>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>Valor previsto (R$) superado</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Muito acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -1607,27 +1966,39 @@
         <v>0.01564514619986043</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>34040564.92</v>
       </c>
       <c r="E32">
-        <v>2025</v>
+        <v>13</v>
+      </c>
+      <c r="F32">
+        <v>2025</v>
+      </c>
+      <c r="G32">
+        <v>0.006107437129531464</v>
+      </c>
+      <c r="H32">
+        <v>-0.009537709070328968</v>
       </c>
       <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Valor previsto (R$) superado</t>
-        </is>
+        <v>-0.6096273533330134</v>
+      </c>
+      <c r="J32">
+        <v>87200179.65049389</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Valor previsto (R$) nao atingido</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Muito abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -1646,27 +2017,39 @@
         <v>0.08227494643576272</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>582641353.6799999</v>
       </c>
       <c r="E33">
-        <v>2025</v>
+        <v>22</v>
+      </c>
+      <c r="F33">
+        <v>2025</v>
+      </c>
+      <c r="G33">
+        <v>0.104535440144091</v>
+      </c>
+      <c r="H33">
+        <v>0.02226049370832832</v>
       </c>
       <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr">
+        <v>0.2705622388427624</v>
+      </c>
+      <c r="J33">
+        <v>458569707.0697411</v>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>Valor previsto (R$) superado</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Dentro do IDRGP Alvo</t>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
     </row>
